--- a/artfynd/A 28698-2025 artfynd.xlsx
+++ b/artfynd/A 28698-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133126965</v>
+        <v>133126963</v>
       </c>
       <c r="B2" t="n">
-        <v>93216</v>
+        <v>92245</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>581925</v>
+        <v>581950</v>
       </c>
       <c r="R2" t="n">
-        <v>7026494</v>
+        <v>7026467</v>
       </c>
       <c r="S2" t="n">
         <v>30</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133126963</v>
+        <v>133126884</v>
       </c>
       <c r="B3" t="n">
-        <v>92227</v>
+        <v>91974</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>581950</v>
+        <v>581956</v>
       </c>
       <c r="R3" t="n">
-        <v>7026467</v>
+        <v>7026421</v>
       </c>
       <c r="S3" t="n">
         <v>30</v>
@@ -859,11 +859,6 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>Camilla Pakka</t>
-        </is>
-      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
@@ -872,17 +867,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Camilla Pakka</t>
+          <t>Via Emmy Ransgart</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133126964</v>
+        <v>133126965</v>
       </c>
       <c r="B4" t="n">
-        <v>79334</v>
+        <v>93271</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,21 +885,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -914,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>581933</v>
+        <v>581925</v>
       </c>
       <c r="R4" t="n">
-        <v>7026473</v>
+        <v>7026494</v>
       </c>
       <c r="S4" t="n">
         <v>30</v>
@@ -984,11 +979,11 @@
         <v>133126885</v>
       </c>
       <c r="B5" t="n">
-        <v>79334</v>
+        <v>79373</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1075,6 +1070,108 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>133126964</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Edsele, Ång</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>581933</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7026473</v>
+      </c>
+      <c r="S6" t="n">
+        <v>30</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Edsele</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>Camilla Pakka</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Emmy Ransgart</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Camilla Pakka</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 28698-2025 artfynd.xlsx
+++ b/artfynd/A 28698-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133126963</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -871,6 +881,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133126884</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -973,6 +988,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133126965</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1070,6 +1090,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133126885</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1172,8 +1197,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133126964</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>